--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G242"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1128,24 +1128,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>חָדָשׁ</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>חֲדָשָׁה</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>חֲדָשִׁים</t>
-        </is>
-      </c>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>חֲדָשׁוֹת</t>
@@ -1154,24 +1142,24 @@
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>plural noun</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>life</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>חֲדָשׁוֹת</t>
-        </is>
-      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>חַיִּים</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -1182,62 +1170,58 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>life</t>
+          <t>challah</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>חַיִּים</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>חַלָּה</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>חַלּוֹת</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>plural noun</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>challah</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr"/>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>חַלָּה</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>חַלּוֹת</t>
-        </is>
-      </c>
+          <t>bill; account</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>חֶשְׁבּוֹן</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>חֶשְׁבּוֹנוֹת</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>bill; account</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>חֶשְׁבּוֹן</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>חֶשְׁבּוֹנוֹת</t>
-        </is>
-      </c>
+          <t>television</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>טֵלֶוִיזְיָה</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
@@ -1245,16 +1229,20 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>television</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr"/>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>טֵלֶוִיזְיָה</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>יָמִים</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
@@ -1262,51 +1250,39 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>old</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>יָשָׁן</t>
-        </is>
-      </c>
+          <t>Yiddish</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>יְשָׁנָה</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>יְשָׁנִים</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>יְשָׁנוֹת</t>
-        </is>
-      </c>
+          <t>יִידִישׁ</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>language</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>יוֹם</t>
+          <t>יַיִן</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>יָמִים</t>
+          <t>יֵינוֹת</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1316,60 +1292,60 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Yiddish</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>יִידִישׁ</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>boy</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>יֶלֶד</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>יְלָדִים</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>wine</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>יַיִן</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>יֵינוֹת</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>girl</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>יַלְדָּה</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>יְלָדוֹת</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>boy</t>
+          <t>sea</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>יֶלֶד</t>
+          <t>יָם</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>יְלָדִים</t>
+          <t>יַמִּים</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1379,179 +1355,155 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>girl</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>יַלְדָּה</t>
-        </is>
-      </c>
+          <t>right side</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>יָמִין</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>יְלָדוֹת</t>
-        </is>
-      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>יָם</t>
+          <t>יַרְדֵּן</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>יַמִּים</t>
-        </is>
-      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>right side</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>יָמִין</t>
+          <t>יִשְׂרָאֵל</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>expensive</t>
+          <t>money</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>יָקָר</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>יְקָרָה</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>יְקָרִים</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>יְקָרוֹת</t>
-        </is>
-      </c>
+          <t>כֶּסֶף</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>fun</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>יַרְדֵּן</t>
+          <t>כֵּיף</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>כֵּיפִים</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>colloquial plural</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>יָשָׁר</t>
-        </is>
-      </c>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>יְשָׁרָה</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>יְשָׁרִים</t>
-        </is>
-      </c>
+          <t>כִּתָּה</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>יְשָׁרוֹת</t>
+          <t>כִּתּוֹת</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>night</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>יִשְׂרָאֵל</t>
+          <t>לַיְלָה</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>לֵילוֹת</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>proper noun</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>כֶּסֶף</t>
+          <t>לֶחֶם</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr"/>
@@ -1563,116 +1515,112 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>kosher</t>
+          <t>lemon</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>כָּשֵׁר</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>כְּשֵׁרָה</t>
-        </is>
-      </c>
+          <t>לִימוֹן</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>כְּשֵׁרִים</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>כְּשֵׁרוֹת</t>
-        </is>
-      </c>
+          <t>לִימוֹנִים</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>fun</t>
+          <t>number</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>כֵּיף</t>
+          <t>מִסְפָּר</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>כֵּיפִים</t>
+          <t>מִסְפָּרִים</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>colloquial plural</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr"/>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>כִּתָּה</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>כִּתּוֹת</t>
-        </is>
-      </c>
+          <t>accent</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>מִבְטָא</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>מִבְטָאִים</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>night</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>לַיְלָה</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
+          <t>מוֹרֶה</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>מוֹרָה</t>
+        </is>
+      </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>לֵילוֹת</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>מוֹרִים</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>מוֹרוֹת</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>לֶחֶם</t>
+          <t>מַחְשֵׁב</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>מַחְשְׁבִים</t>
+        </is>
+      </c>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
@@ -1680,18 +1628,18 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>lemon</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>לִימוֹן</t>
+          <t>מִטְבָּח</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>לִימוֹנִים</t>
+          <t>מִטְבָּחִים</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -1701,122 +1649,98 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>special</t>
+          <t>mayonnaise</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>מְיֻחָד</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>מְיֻחֶדֶת</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>מְיֻחָדִים</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>מְיֻחָדוֹת</t>
-        </is>
-      </c>
+          <t>מָיוֹנֵז</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>מִסְפָּר</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>מִסְפָּרִים</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+          <t>bed</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>מִטָּה</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>מִטּוֹת</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>accent</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>מִבְטָא</t>
-        </is>
-      </c>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>מִבְטָאִים</t>
+          <t>מַיִם</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>plural noun</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>teacher</t>
+          <t>letter</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>מוֹרֶה</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>מוֹרָה</t>
-        </is>
-      </c>
+          <t>מִכְתָּב</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>מוֹרִים</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>מוֹרוֹת</t>
-        </is>
-      </c>
+          <t>מִכְתָּבִים</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>computer</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>מַחְשֵׁב</t>
+          <t>מָלוֹן</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>מַחְשְׁבִים</t>
+          <t>מְלוֹנוֹת</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -1826,20 +1750,16 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>kitchen</t>
+          <t>salt</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>מִטְבָּח</t>
+          <t>מֶלַח</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>מִטְבָּחִים</t>
-        </is>
-      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
@@ -1847,100 +1767,108 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>mayonnaise</t>
+          <t>waiter</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>מָיוֹנֵז</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
+          <t>מֶלְצַר</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>מֶלְצָרִית</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>מֶלְצָרִים</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>מֶלְצָרִיּוֹת</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>bed</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>מִטָּה</t>
-        </is>
-      </c>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>נַעְנָע</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>מִטּוֹת</t>
-        </is>
-      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>herb</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>מַיִם</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>מִסְעָדָה</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>מִסְעָדוֹת</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>plural noun</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>letter</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>מִכְתָּב</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>מִכְתָּבִים</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>shower</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>מִקְלַחַת</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>מִקְלָחוֹת</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>מָלוֹן</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>מְלוֹנוֹת</t>
-        </is>
-      </c>
+          <t>margarine</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>מַרְגָּרִינָה</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
@@ -1948,44 +1876,40 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>salt</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>מֶלַח</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>מִשְׁפָּחָה</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>מִשְׁפָּחוֹת</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>waiter</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>מֶלְצַר</t>
-        </is>
-      </c>
+          <t>gift</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>מֶלְצָרִית</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>מֶלְצָרִים</t>
-        </is>
-      </c>
+          <t>מַתָּנָה</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>מֶלְצָרִיּוֹת</t>
+          <t>מַתָּנוֹת</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -1994,40 +1918,52 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>female</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>נַעְנָע</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>נָקֵב</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>נְקֵבָה</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>נְקֵבִים</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>נְקֵבוֹת</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>herb</t>
+          <t>biological sex</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>library</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>מִסְעָדָה</t>
+          <t>סִפְרִיָּה</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>מִסְעָדוֹת</t>
+          <t>סִפְרִיּוֹת</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -2036,52 +1972,44 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>מְצֻיָּן</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>מְצֻיֶּנֶת</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>מְצֻיָּנִים</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>מְצֻיָּנוֹת</t>
-        </is>
-      </c>
+          <t>סֻכָּר</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>shower</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr"/>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>סְטוּדֶנְט</t>
+        </is>
+      </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>מִקְלַחַת</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
+          <t>סְטוּדֶנְטִית</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>סְטוּדֶנְטִים</t>
+        </is>
+      </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>מִקְלָחוֹת</t>
+          <t>סְטוּדֶנְטִיּוֹת</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -2090,16 +2018,20 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>margarine</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>מַרְגָּרִינָה</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>living room</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>סָלוֹן</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>סָלוֹנִים</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
@@ -2107,40 +2039,40 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>family</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>מִשְׁפָּחָה</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>מִשְׁפָּחוֹת</t>
-        </is>
-      </c>
+          <t>salad</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>סָלָט</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>סָלָטִים</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>gift</t>
+          <t>apology</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>מַתָּנָה</t>
+          <t>סְלִיחָה</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>מַתָּנוֹת</t>
+          <t>סְלִיחוֹת</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -2149,205 +2081,165 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>film</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>נָכוֹן</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>נְכוֹנָה</t>
-        </is>
-      </c>
+          <t>סֶרֶט</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>נְכוֹנִים</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>נְכוֹנוֹת</t>
-        </is>
-      </c>
+          <t>סְרָטִים</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>pleasant</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>נָעִים</t>
-        </is>
-      </c>
+          <t>work; job</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>נְעִימָה</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>נְעִימִים</t>
-        </is>
-      </c>
+          <t>עֲבוֹדָה</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>נְעִימוֹת</t>
+          <t>עֲבוֹדוֹת</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>tree</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>נָקֵב</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>נְקֵבָה</t>
-        </is>
-      </c>
+          <t>עֵץ</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>נְקֵבִים</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>נְקֵבוֹת</t>
-        </is>
-      </c>
+          <t>עֵצִים</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>biological sex</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>library</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>סִפְרִיָּה</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>סִפְרִיּוֹת</t>
-        </is>
-      </c>
+          <t>evening</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>עֶרֶב</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>עֲרָבִים</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>sugar</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>סֻכָּר</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
+          <t>cake</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>עוּגָה</t>
+        </is>
+      </c>
       <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>עוּגוֹת</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>student</t>
+          <t>world</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>סְטוּדֶנְט</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>סְטוּדֶנְטִית</t>
-        </is>
-      </c>
+          <t>עוֹלָם</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>סְטוּדֶנְטִים</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>סְטוּדֶנְטִיּוֹת</t>
-        </is>
-      </c>
+          <t>עוֹלָמוֹת</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>living room</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>סָלוֹן</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>סָלוֹנִים</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>עִיר</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>עָרִים</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>salad</t>
+          <t>drawing</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>סָלָט</t>
+          <t>צִיּוּר</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>סָלָטִים</t>
+          <t>צִיּוּרִים</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -2357,41 +2249,37 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>apology</t>
+          <t>noon; afternoon</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>סְלִיחָה</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>סְלִיחוֹת</t>
-        </is>
-      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>צָהֳרַיִם</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>plural noun</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>film</t>
+          <t>coffee; café</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>סֶרֶט</t>
+          <t>קָפֶה</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>סְרָטִים</t>
-        </is>
-      </c>
+      <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr"/>
@@ -2399,39 +2287,39 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>work; job</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>עֲבוֹדָה</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>עֲבוֹדוֹת</t>
-        </is>
-      </c>
+          <t>street</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>רְחוֹב</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>רְחוֹבוֹת</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>tree</t>
+          <t>quarter</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>עֵץ</t>
+          <t>רֶבַע</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>עֵצִים</t>
+          <t>רְבָעִים</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -2441,18 +2329,18 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>moment</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>עֶרֶב</t>
+          <t>רֶגַע</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>עֲרָבִים</t>
+          <t>רְגָעִים</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -2462,81 +2350,77 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>cake</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>עוּגָה</t>
-        </is>
-      </c>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>רַדְיוֹ</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>עוּגוֹת</t>
-        </is>
-      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>world</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>עוֹלָם</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>עוֹלָמוֹת</t>
-        </is>
-      </c>
+          <t>Romanian</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>רוֹמָנִית</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>toilets</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>עִיר</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>עָרִים</t>
-        </is>
-      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>שֵׁירוּתִים</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>plural noun</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>drawing</t>
+          <t>table</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>צִיּוּר</t>
+          <t>שֻׁלְחָן</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>צִיּוּרִים</t>
+          <t>שֻׁלְחָנוֹת</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -2546,103 +2430,83 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>noon; afternoon</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr"/>
+          <t>lesson</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>שִׁיעוּר</t>
+        </is>
+      </c>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>צָהֳרַיִם</t>
+          <t>שִׁיעוּרִים</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>plural noun</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>public</t>
+          <t>song</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>צִבּוּרִי</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>צִבּוּרִית</t>
-        </is>
-      </c>
+          <t>שִׁיר</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>צִבּוּרִיִּים</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>צִבּוּרִיּוֹת</t>
-        </is>
-      </c>
+          <t>שִׁירִים</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>קָטָן</t>
-        </is>
-      </c>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>קְטַנָּה</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>קְטַנִּים</t>
-        </is>
-      </c>
+          <t>שֶׁמֶשׁ</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>קְטַנּוֹת</t>
+          <t>שְׁמָשׁוֹת</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>coffee; café</t>
+          <t>clock</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>קָפֶה</t>
+          <t>שָׁעוֹן</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr"/>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>שְׁעוֹנִים</t>
+        </is>
+      </c>
       <c r="E97" s="2" t="inlineStr"/>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr"/>
@@ -2650,20 +2514,16 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>street</t>
+          <t>quiet</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>רְחוֹב</t>
+          <t>שֶׁקֶט</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>רְחוֹבוֹת</t>
-        </is>
-      </c>
+      <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr"/>
@@ -2671,54 +2531,62 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>quarter</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>רֶבַע</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>רְבָעִים</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
+          <t>passion</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>תְּשׁוּקָה</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>תְּשׁוּקוֹת</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>moment</t>
+          <t>pupil</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>רֶגַע</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr"/>
+          <t>תַּלְמִיד</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>תַּלְמִידָה</t>
+        </is>
+      </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>רְגָעִים</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
+          <t>תַּלְמִידִים</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>תַּלְמִידוֹת</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>radio</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>רַדְיוֹ</t>
+          <t>תֵּה</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr"/>
@@ -2730,81 +2598,81 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Romanian</t>
+          <t>thanks</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>רוֹמָנִית</t>
+          <t>תּוֹדָה</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>תּוֹדוֹת</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>toilets</t>
+          <t>feeling</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr"/>
-      <c r="C103" s="2" t="inlineStr"/>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>שֵׁירוּתִים</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>תְּחוּשָׁה</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>תְּחוּשׁוֹת</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>plural noun</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>שֻׁלְחָן</t>
+          <t>תֵּימָן</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>שֻׁלְחָנוֹת</t>
-        </is>
-      </c>
+      <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>lesson</t>
+          <t>date fruit</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>שִׁיעוּר</t>
+          <t>תָּמָר</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>שִׁיעוּרִים</t>
+          <t>תְּמָרִים</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -2814,18 +2682,18 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>song</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>שִׁיר</t>
+          <t>תַּפְרִיט</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr"/>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>שִׁירִים</t>
+          <t>תַּפְרִיטִים</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -2835,19 +2703,19 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>example</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>שֶׁמֶשׁ</t>
+          <t>דֻּגְמָה</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>שְׁמָשׁוֹת</t>
+          <t>דֻּגְמָאוֹת</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -2856,18 +2724,18 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>clock</t>
+          <t>shopping mall</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>שָׁעוֹן</t>
+          <t>קַנְיוֹן</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr"/>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>שְׁעוֹנִים</t>
+          <t>קַנְיוֹנִים</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -2877,65 +2745,69 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>quiet</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>שֶׁקֶט</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr"/>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>שְׁאֵלָה</t>
+        </is>
+      </c>
       <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>שְׁאֵלוֹת</t>
+        </is>
+      </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>passion</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr"/>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>תְּשׁוּקָה</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>תְּשׁוּקוֹת</t>
-        </is>
-      </c>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>צֶבַע</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>צְבָעִים</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>pupil</t>
+          <t>prophet</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>תַּלְמִיד</t>
+          <t>נָבִיא</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>תַּלְמִידָה</t>
+          <t>נְבִיאָה</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>תַּלְמִידִים</t>
+          <t>נְבִיאִים</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>תַּלְמִידוֹת</t>
+          <t>נְבִיאוֹת</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -2944,680 +2816,536 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>tea</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>תֵּה</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr"/>
+          <t>lettuce</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>חֲסָה</t>
+        </is>
+      </c>
       <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="2" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>חֲסוֹת</t>
+        </is>
+      </c>
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>thanks</t>
+          <t>but</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr"/>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>תּוֹדָה</t>
-        </is>
-      </c>
+      <c r="C113" s="2" t="inlineStr"/>
       <c r="D113" s="2" t="inlineStr"/>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>תּוֹדוֹת</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>אֲבָל</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>particle</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>feeling</t>
+          <t>never mind</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr"/>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>תְּחוּשָׁה</t>
-        </is>
-      </c>
+      <c r="C114" s="2" t="inlineStr"/>
       <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>תְּחוּשׁוֹת</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>אֵין דָּבָר</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Yemen</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>תֵּימָן</t>
-        </is>
-      </c>
+          <t>can I get</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr"/>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>אֶפְשָׁר לְקַבֵּל</t>
+        </is>
+      </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>date fruit</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>תָּמָר</t>
-        </is>
-      </c>
+          <t>or</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>תְּמָרִים</t>
-        </is>
-      </c>
+      <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>אוֹ</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>particle</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>תַּפְרִיט</t>
-        </is>
-      </c>
+          <t>maybe</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr"/>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>תַּפְרִיטִים</t>
-        </is>
-      </c>
+      <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>אוּלַי</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>nice</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>נֶחְמָד</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>נֶחְמָדָה</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>נֶחְמָדִים</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>נֶחְמָדוֹת</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr"/>
+          <t>so, then</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr"/>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>אָז</t>
+        </is>
+      </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>adverb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>interesting</t>
+          <t>1 (masc.)</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>מְעַנְיֵן</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>מְעַנְיֶנֶת</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>מְעַנְיְנִים</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>מְעַנְיְנוֹת</t>
-        </is>
-      </c>
+          <t>אֶחָד</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>boring</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>מְשַׁעֲמֵם</t>
-        </is>
-      </c>
+          <t>1 (fem.)</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>מְשַׁעֲמֶמֶת</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>מְשַׁעֲמְמִים</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>מְשַׁעֲמְמוֹת</t>
-        </is>
-      </c>
+          <t>אַחַת</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>what luck</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr"/>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>דֻּגְמָה</t>
-        </is>
-      </c>
+      <c r="C121" s="2" t="inlineStr"/>
       <c r="D121" s="2" t="inlineStr"/>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>דֻּגְמָאוֹת</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>אֵיזֶה מַזָּל</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>shopping mall</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>קַנְיוֹן</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>קַנְיוֹנִים</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
+          <t>mother</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>אִמָּא</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>אִמָּהוֹת</t>
+        </is>
+      </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>שְׁאֵלָה</t>
+          <t>אִירְלַנְד</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr"/>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>שְׁאֵלוֹת</t>
-        </is>
-      </c>
+      <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>proper noun</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>man</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>אָדֹם</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>אֲדֻמָּה</t>
-        </is>
-      </c>
+          <t>אִישׁ</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>אֲדֻמִּים</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>אֲדֻמּוֹת</t>
-        </is>
-      </c>
+          <t>אֲנָשִׁים</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>כָּתֹום</t>
-        </is>
-      </c>
+          <t>woman</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>כְּתֻמָּה</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>כְּתֻמִּים</t>
-        </is>
-      </c>
+          <t>אִשָּׁה</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>כְּתֻמּוֹת</t>
+          <t>נָשִׁים</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>yellow</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>צָהֹוב</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>צְהֻבָּה</t>
-        </is>
-      </c>
+          <t>these</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>צְהֻבִּים</t>
+          <t>אֵלֶּה</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>צְהֻבּוֹת</t>
+          <t>אֵלֶּה</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>שָׁחֹור</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>שְׁחוֹרָה</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>שְׁחוֹרִים</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>שְׁחוֹרוֹת</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr"/>
+          <t>to me</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>אֵלַי</t>
+        </is>
+      </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>preposition</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>כָּחֹול</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>כְּחֻלָּה</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>כְּחֻלִּים</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>כְּחֻלּוֹת</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>אֲנִי</t>
+        </is>
+      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>brown</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>חוּם</t>
-        </is>
-      </c>
+          <t>0 (fem.)</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>חוּמָה</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>חוּמִים</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>חוּמוֹת</t>
-        </is>
-      </c>
+          <t>אֶפֶס</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>grey</t>
+          <t>0 (masc.)</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>אָפֹור</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>אֲפֹורָה</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>אֲפֹורִים</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>אֲפֹורוֹת</t>
-        </is>
-      </c>
+          <t>אֶפֶס</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>4 (masc.)</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>יָרֹוק</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>יְרֻקָּה</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>יְרֻקִּים</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>יְרֻקּוֹת</t>
-        </is>
-      </c>
+          <t>אַרְבָּעָה</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr"/>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>white</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>לָבָן</t>
-        </is>
-      </c>
+          <t>4 (fem.)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>לְבָנָה</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>לְבָנִים</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>לְבָנוֹת</t>
-        </is>
-      </c>
+          <t>אַרְבַּע</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>צֶבַע</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr"/>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>צְבָעִים</t>
-        </is>
-      </c>
+          <t>you (fem.)</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>אַתְּ</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>prophet</t>
+          <t>you (masc.)</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>נָבִיא</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>נְבִיאָה</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>נְבִיאִים</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>נְבִיאוֹת</t>
-        </is>
-      </c>
+          <t>אַתָּה</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>lettuce</t>
+          <t>you (pl. masc.)</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr"/>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>חֲסָה</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>חֲסוֹת</t>
-        </is>
-      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>אַתֶּם</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>you (pl. fem.)</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>אֲבָל</t>
-        </is>
-      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>אַתֶּן</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>particle</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>how</t>
+          <t>without</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr"/>
@@ -3626,19 +3354,19 @@
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>אֵיךְ</t>
+          <t>בְּלִי</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>question word</t>
+          <t>preposition</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>never mind</t>
+          <t>alright</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr"/>
@@ -3647,7 +3375,7 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>אֵין דָּבָר</t>
+          <t>בְּסֵדֶר</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -3659,7 +3387,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>can I get</t>
+          <t>also</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr"/>
@@ -3668,40 +3396,40 @@
       <c r="E139" s="2" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>אֶפְשָׁר לְקַבֵּל</t>
+          <t>גַּם</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>adverb</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>she</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr"/>
-      <c r="C140" s="2" t="inlineStr"/>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>הִיא</t>
+        </is>
+      </c>
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>אוֹ</t>
-        </is>
-      </c>
+      <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>particle</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr"/>
@@ -3710,7 +3438,7 @@
       <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>אוּלַי</t>
+          <t>הַיּוֹם</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -3722,7 +3450,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>so, then</t>
+          <t>there (behold)</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr"/>
@@ -3731,130 +3459,134 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>אָז</t>
+          <t>הִנֵּה</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>adverb</t>
+          <t>particle</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>1 (masc.)</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>אֶחָד</t>
-        </is>
-      </c>
+          <t>everything</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr"/>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>הַכֹּל</t>
+        </is>
+      </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>1 (fem.)</t>
+          <t>they (masc.)</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr"/>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>אַחַת</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr"/>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>הֵם</t>
+        </is>
+      </c>
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>what luck</t>
+          <t>they (fem.)</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr"/>
       <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>אֵיזֶה מַזָּל</t>
-        </is>
-      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>הֵן</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>many</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr"/>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>אִמָּא</t>
-        </is>
-      </c>
+      <c r="C146" s="2" t="inlineStr"/>
       <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>אִמָּהוֹת</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>הַרְבֵּה</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>quantifier</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>where</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr"/>
-      <c r="C147" s="2" t="inlineStr"/>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>הַשָּׁעָה</t>
+        </is>
+      </c>
       <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>אֵיפֹה</t>
-        </is>
-      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>הַשָּׁעוֹת</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>question word</t>
+          <t>with article</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>this (fem.)</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>אִירְלַנְד</t>
+          <t>זֹאת</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr"/>
@@ -3862,170 +3594,166 @@
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>man</t>
+          <t>this (masc.)</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>אִישׁ</t>
+          <t>זֶה</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr"/>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>אֲנָשִׁים</t>
-        </is>
-      </c>
+      <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>pronoun</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>woman</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr"/>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>אִשָּׁה</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>נָשִׁים</t>
-        </is>
-      </c>
+          <t>masculine</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>זָכָר</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>זְכָרִים</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>these</t>
+          <t>bun</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr"/>
-      <c r="C151" s="2" t="inlineStr"/>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>אֵלֶּה</t>
-        </is>
-      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>חַלָּה</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>אֵלֶּה</t>
+          <t>חַלּוֹת</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>pronoun</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>to me</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr"/>
+          <t>5 (masc.)</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>חֲמִשָּׁה</t>
+        </is>
+      </c>
       <c r="C152" s="2" t="inlineStr"/>
       <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>אֵלַי</t>
-        </is>
-      </c>
+      <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>preposition</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>5 (fem.)</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr"/>
-      <c r="C153" s="2" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>חָמֵשׁ</t>
+        </is>
+      </c>
       <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>אֲנִי</t>
-        </is>
-      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>0 (fem.)</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr"/>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>אֶפֶס</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
+          <t>half</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>חֵצִי</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>חֲצָאִים</t>
+        </is>
+      </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>0 (masc.)</t>
+          <t>bill</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>אֶפֶס</t>
+          <t>חֶשְׁבּוֹן</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr"/>
-      <c r="D155" s="2" t="inlineStr"/>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>חֶשְׁבּוֹנוֹת</t>
+        </is>
+      </c>
       <c r="E155" s="2" t="inlineStr"/>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>4 (masc.)</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>אַרְבָּעָה</t>
+          <t>יוֹם חֲמִישִׁי</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr"/>
@@ -4034,61 +3762,61 @@
       <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>4 (fem.)</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr"/>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>אַרְבַּע</t>
-        </is>
-      </c>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם רְבִיעִי</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="2" t="inlineStr"/>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>you (fem.)</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr"/>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>אַתְּ</t>
-        </is>
-      </c>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם רִאשׁוֹן</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>you (masc.)</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>אַתָּה</t>
+          <t>יוֹם שְׁלִישִׁי</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr"/>
@@ -4097,131 +3825,119 @@
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>you (pl. masc.)</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr"/>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם שִׁישִׁי</t>
+        </is>
+      </c>
       <c r="C160" s="2" t="inlineStr"/>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>אַתֶּם</t>
-        </is>
-      </c>
+      <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>you (pl. fem.)</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr"/>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>יוֹם שֵׁנִי</t>
+        </is>
+      </c>
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr"/>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>אַתֶּן</t>
-        </is>
-      </c>
+      <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>of course, sure</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>בָּטוּחַ</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>בְּטוּחָה</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>בְּטוּחִים</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>בְּטוּחוֹת</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr"/>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr"/>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>שַׁבָּת</t>
+        </is>
+      </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>adjective</t>
+          <t>weekday</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>without</t>
+          <t>yiddish</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr"/>
-      <c r="C163" s="2" t="inlineStr"/>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>יִידִישׁ</t>
+        </is>
+      </c>
       <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>בְּלִי</t>
-        </is>
-      </c>
+      <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>preposition</t>
+          <t>language</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>alright</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr"/>
+          <t>right (side)</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>יָמִין</t>
+        </is>
+      </c>
       <c r="C164" s="2" t="inlineStr"/>
       <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>בְּסֵדֶר</t>
-        </is>
-      </c>
+      <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>direction</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>also</t>
+          <t>rightwards</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr"/>
@@ -4230,82 +3946,90 @@
       <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>גַּם</t>
+          <t>יָמִינָה</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>adverb</t>
+          <t>direction</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>she</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr"/>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>הִיא</t>
-        </is>
-      </c>
+          <t>israel</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>יִשְׂרָאֵל</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr"/>
       <c r="D166" s="2" t="inlineStr"/>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>proper noun</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>everybody</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr"/>
       <c r="C167" s="2" t="inlineStr"/>
-      <c r="D167" s="2" t="inlineStr"/>
-      <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>הַיּוֹם</t>
-        </is>
-      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>כֻּלָּם</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>כֻּלָּן</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>adverb</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>there (behold)</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr"/>
       <c r="C168" s="2" t="inlineStr"/>
-      <c r="D168" s="2" t="inlineStr"/>
-      <c r="E168" s="2" t="inlineStr"/>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>הִנֵּה</t>
-        </is>
-      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>כֻּלָּם</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>כֻּלָּן</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>particle</t>
+          <t>pronoun</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>everything</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr"/>
@@ -4314,61 +4038,61 @@
       <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>הַכֹּל</t>
+          <t>כָּל</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>quantifier</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>they (masc.)</t>
+          <t>the whole thing</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr"/>
       <c r="C170" s="2" t="inlineStr"/>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>הֵם</t>
-        </is>
-      </c>
+      <c r="D170" s="2" t="inlineStr"/>
       <c r="E170" s="2" t="inlineStr"/>
-      <c r="F170" s="2" t="inlineStr"/>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>כָּל הַקֶּטַע</t>
+        </is>
+      </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>they (fem.)</t>
+          <t>no</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr"/>
       <c r="C171" s="2" t="inlineStr"/>
       <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>הֵן</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>לֹא</t>
+        </is>
+      </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>particle</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>many</t>
+          <t>see you</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr"/>
@@ -4377,338 +4101,334 @@
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>הַרְבֵּה</t>
+          <t>לְהִתְרָאוֹת</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>quantifier</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>near</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr"/>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>הַשָּׁעָה</t>
-        </is>
-      </c>
+      <c r="C173" s="2" t="inlineStr"/>
       <c r="D173" s="2" t="inlineStr"/>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>הַשָּׁעוֹת</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>לְיַד</t>
+        </is>
+      </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>with article</t>
+          <t>preposition</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>this (fem.)</t>
+          <t>very</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr"/>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>זֹאת</t>
-        </is>
-      </c>
+      <c r="C174" s="2" t="inlineStr"/>
       <c r="D174" s="2" t="inlineStr"/>
       <c r="E174" s="2" t="inlineStr"/>
-      <c r="F174" s="2" t="inlineStr"/>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>מְאֹד</t>
+        </is>
+      </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>adverb</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>this (masc.)</t>
+          <t>teacher (masc.)</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>זֶה</t>
+          <t>מוֹרֶה</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr"/>
-      <c r="D175" s="2" t="inlineStr"/>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>מוֹרִים</t>
+        </is>
+      </c>
       <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>pronoun</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>masculine</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>זָכָר</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr"/>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>זְכָרִים</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr"/>
+          <t>teacher (fem.)</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>מוֹרָה</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>מוֹרוֹת</t>
+        </is>
+      </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>bun</t>
+          <t>nice to meet you</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr"/>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>חַלָּה</t>
-        </is>
-      </c>
+      <c r="C177" s="2" t="inlineStr"/>
       <c r="D177" s="2" t="inlineStr"/>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>חַלּוֹת</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>נָעִים מְאֹד</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>phrase</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>5 (masc.)</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>חֲמִשָּׁה</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr"/>
+          <t>feminine</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>נְקֵבָה</t>
+        </is>
+      </c>
       <c r="D178" s="2" t="inlineStr"/>
-      <c r="E178" s="2" t="inlineStr"/>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>נְקֵבוֹת</t>
+        </is>
+      </c>
       <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>5 (fem.)</t>
+          <t>excuse me</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr"/>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>חָמֵשׁ</t>
-        </is>
-      </c>
+      <c r="C179" s="2" t="inlineStr"/>
       <c r="D179" s="2" t="inlineStr"/>
       <c r="E179" s="2" t="inlineStr"/>
-      <c r="F179" s="2" t="inlineStr"/>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>סְלִיחָה</t>
+        </is>
+      </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>half</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>חֵצִי</t>
-        </is>
-      </c>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr"/>
       <c r="C180" s="2" t="inlineStr"/>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>חֲצָאִים</t>
-        </is>
-      </c>
+      <c r="D180" s="2" t="inlineStr"/>
       <c r="E180" s="2" t="inlineStr"/>
-      <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr"/>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>עַכְשָׁיו</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>adverb</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>bill</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>חֶשְׁבּוֹן</t>
-        </is>
-      </c>
+          <t>about</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr"/>
       <c r="C181" s="2" t="inlineStr"/>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>חֶשְׁבּוֹנוֹת</t>
-        </is>
-      </c>
+      <c r="D181" s="2" t="inlineStr"/>
       <c r="E181" s="2" t="inlineStr"/>
-      <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr"/>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>עַל</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>preposition</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>יוֹם חֲמִישִׁי</t>
-        </is>
-      </c>
+          <t>with</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr"/>
       <c r="C182" s="2" t="inlineStr"/>
       <c r="D182" s="2" t="inlineStr"/>
       <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="inlineStr"/>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>עִם</t>
+        </is>
+      </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>preposition</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>יוֹם רְבִיעִי</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr"/>
+          <t>עֲשָׂרָה</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>עֶשֶׂר</t>
+        </is>
+      </c>
       <c r="D183" s="2" t="inlineStr"/>
       <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>יוֹם רִאשׁוֹן</t>
-        </is>
-      </c>
+          <t>here</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr"/>
       <c r="C184" s="2" t="inlineStr"/>
       <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr"/>
+      <c r="F184" s="3" t="inlineStr">
+        <is>
+          <t>פֹּה</t>
+        </is>
+      </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>adverb</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>painting</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>יוֹם שְׁלִישִׁי</t>
+          <t>צִיּוּר</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr"/>
-      <c r="D185" s="2" t="inlineStr"/>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>צִיּוּרִים</t>
+        </is>
+      </c>
       <c r="E185" s="2" t="inlineStr"/>
       <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>יוֹם שִׁישִׁי</t>
-        </is>
-      </c>
+          <t>afternoon</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr"/>
       <c r="C186" s="2" t="inlineStr"/>
-      <c r="D186" s="2" t="inlineStr"/>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>צָהֳרַיִם</t>
+        </is>
+      </c>
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>plural noun</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>café</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>יוֹם שֵׁנִי</t>
+          <t>קָפֶה</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr"/>
       <c r="D187" s="2" t="inlineStr"/>
       <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>weekday</t>
-        </is>
-      </c>
+      <c r="G187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>some</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr"/>
@@ -4717,25 +4437,25 @@
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>שַׁבָּת</t>
+          <t>קְצָת</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>weekday</t>
+          <t>quantifier</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>yiddish</t>
+          <t>romanian</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr"/>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>יִידִישׁ</t>
+          <t>רוֹמָנִית</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr"/>
@@ -4750,28 +4470,28 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>right (side)</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>יָמִין</t>
-        </is>
-      </c>
+          <t>only, just</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr"/>
       <c r="C190" s="2" t="inlineStr"/>
       <c r="D190" s="2" t="inlineStr"/>
       <c r="E190" s="2" t="inlineStr"/>
-      <c r="F190" s="2" t="inlineStr"/>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>רַק</t>
+        </is>
+      </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>adverb</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>rightwards</t>
+          <t>just a moment</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr"/>
@@ -4780,111 +4500,111 @@
       <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>יָמִינָה</t>
+          <t>רַק רֶגַע</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>israel</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>יִשְׂרָאֵל</t>
-        </is>
-      </c>
+          <t>leftwards</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr"/>
       <c r="C192" s="2" t="inlineStr"/>
       <c r="D192" s="2" t="inlineStr"/>
       <c r="E192" s="2" t="inlineStr"/>
-      <c r="F192" s="2" t="inlineStr"/>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>שְׂמֹאלָה</t>
+        </is>
+      </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>proper noun</t>
+          <t>direction</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>how many</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr"/>
-      <c r="C193" s="2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>שִׁבְעָה</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>שֶׁבַע</t>
+        </is>
+      </c>
       <c r="D193" s="2" t="inlineStr"/>
       <c r="E193" s="2" t="inlineStr"/>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>כַּמָּה</t>
-        </is>
-      </c>
+      <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>question word</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>everybody</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr"/>
-      <c r="C194" s="2" t="inlineStr"/>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>כֻּלָּם</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>כֻּלָּן</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>שִׁשָּׁה</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>שֵׁשׁ</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="inlineStr"/>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>everyone</t>
+          <t>of</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr"/>
       <c r="C195" s="2" t="inlineStr"/>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>כֻּלָּם</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>כֻּלָּן</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr"/>
+      <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>שֶׁל</t>
+        </is>
+      </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>pronoun</t>
+          <t>preposition</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>hello</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr"/>
@@ -4893,40 +4613,44 @@
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>כָּל</t>
+          <t>שָׁלוֹם</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>quantifier</t>
+          <t>greeting</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>the whole thing</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr"/>
-      <c r="C197" s="2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>שְׁלוֹשָׁה</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>שָׁלוֹשׁ</t>
+        </is>
+      </c>
       <c r="D197" s="2" t="inlineStr"/>
       <c r="E197" s="2" t="inlineStr"/>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>כָּל הַקֶּטַע</t>
-        </is>
-      </c>
+      <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>there (direction)</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr"/>
@@ -4935,103 +4659,111 @@
       <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>לֹא</t>
+          <t>שָׁם</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>particle</t>
+          <t>adverb</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>where to</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr"/>
+          <t>left (side)</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>שְׂמֹאל</t>
+        </is>
+      </c>
       <c r="C199" s="2" t="inlineStr"/>
       <c r="D199" s="2" t="inlineStr"/>
       <c r="E199" s="2" t="inlineStr"/>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>לְאָן</t>
-        </is>
-      </c>
+      <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>question word</t>
+          <t>direction</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>see you</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr"/>
-      <c r="C200" s="2" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>שְׁמוֹנָה</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>שְׁמוֹנֶה</t>
+        </is>
+      </c>
       <c r="D200" s="2" t="inlineStr"/>
       <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>לְהִתְרָאוֹת</t>
-        </is>
-      </c>
+      <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>phrase</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr"/>
-      <c r="C201" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>שְׁנַיִם</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>שְׁתַּיִם</t>
+        </is>
+      </c>
       <c r="D201" s="2" t="inlineStr"/>
       <c r="E201" s="2" t="inlineStr"/>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>לְיַד</t>
-        </is>
-      </c>
+      <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>preposition</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>when</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr"/>
-      <c r="C202" s="2" t="inlineStr"/>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>שָׁעָה</t>
+        </is>
+      </c>
       <c r="D202" s="2" t="inlineStr"/>
-      <c r="E202" s="2" t="inlineStr"/>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>מָתַי</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>question word</t>
-        </is>
-      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>שָׁעוֹת</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>thank you</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr"/>
@@ -5040,61 +4772,65 @@
       <c r="E203" s="2" t="inlineStr"/>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>מְאֹד</t>
+          <t>תּוֹדָה</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>adverb</t>
+          <t>phrase</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>where from</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr"/>
+          <t>date (fruit)</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>תָּמָר</t>
+        </is>
+      </c>
       <c r="C204" s="2" t="inlineStr"/>
-      <c r="D204" s="2" t="inlineStr"/>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>תְּמָרִים</t>
+        </is>
+      </c>
       <c r="E204" s="2" t="inlineStr"/>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>מֵאַיִן</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>question word</t>
-        </is>
-      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>from where</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr"/>
-      <c r="C205" s="2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>תִּשְׁעָה</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>תֵּשַׁע</t>
+        </is>
+      </c>
       <c r="D205" s="2" t="inlineStr"/>
       <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>מֵאֵיפֹה</t>
-        </is>
-      </c>
+      <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>question word</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>what</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr"/>
@@ -5103,826 +4839,10 @@
       <c r="E206" s="2" t="inlineStr"/>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>מָה</t>
+          <t>לִפְעָמִים</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>question word</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
-        <is>
-          <t>teacher (masc.)</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="inlineStr">
-        <is>
-          <t>מוֹרֶה</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr"/>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>מוֹרִים</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>teacher (fem.)</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr"/>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>מוֹרָה</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr"/>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>מוֹרוֹת</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>who</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr"/>
-      <c r="C209" s="2" t="inlineStr"/>
-      <c r="D209" s="2" t="inlineStr"/>
-      <c r="E209" s="2" t="inlineStr"/>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>מִי</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>question word</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>right (correct)</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>נָכוֹן</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>נְכוֹנָה</t>
-        </is>
-      </c>
-      <c r="D210" s="3" t="inlineStr">
-        <is>
-          <t>נְכוֹנִים</t>
-        </is>
-      </c>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>נְכוֹנוֹת</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>nice to meet you</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr"/>
-      <c r="C211" s="2" t="inlineStr"/>
-      <c r="D211" s="2" t="inlineStr"/>
-      <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>נָעִים מְאֹד</t>
-        </is>
-      </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>feminine</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr"/>
-      <c r="C212" s="3" t="inlineStr">
-        <is>
-          <t>נְקֵבָה</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr"/>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>נְקֵבוֹת</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>excuse me</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr"/>
-      <c r="C213" s="2" t="inlineStr"/>
-      <c r="D213" s="2" t="inlineStr"/>
-      <c r="E213" s="2" t="inlineStr"/>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>סְלִיחָה</t>
-        </is>
-      </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>now</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr"/>
-      <c r="C214" s="2" t="inlineStr"/>
-      <c r="D214" s="2" t="inlineStr"/>
-      <c r="E214" s="2" t="inlineStr"/>
-      <c r="F214" s="3" t="inlineStr">
-        <is>
-          <t>עַכְשָׁיו</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>adverb</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>about</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr"/>
-      <c r="C215" s="2" t="inlineStr"/>
-      <c r="D215" s="2" t="inlineStr"/>
-      <c r="E215" s="2" t="inlineStr"/>
-      <c r="F215" s="3" t="inlineStr">
-        <is>
-          <t>עַל</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>preposition</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>with</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr"/>
-      <c r="C216" s="2" t="inlineStr"/>
-      <c r="D216" s="2" t="inlineStr"/>
-      <c r="E216" s="2" t="inlineStr"/>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>עִם</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>preposition</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="inlineStr">
-        <is>
-          <t>עֲשָׂרָה</t>
-        </is>
-      </c>
-      <c r="C217" s="3" t="inlineStr">
-        <is>
-          <t>עֶשֶׂר</t>
-        </is>
-      </c>
-      <c r="D217" s="2" t="inlineStr"/>
-      <c r="E217" s="2" t="inlineStr"/>
-      <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>here</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr"/>
-      <c r="C218" s="2" t="inlineStr"/>
-      <c r="D218" s="2" t="inlineStr"/>
-      <c r="E218" s="2" t="inlineStr"/>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>פֹּה</t>
-        </is>
-      </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>adverb</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>painting</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>צִיּוּר</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr"/>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>צִיּוּרִים</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>afternoon</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr"/>
-      <c r="C220" s="2" t="inlineStr"/>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>צָהֳרַיִם</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr"/>
-      <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>plural noun</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>public (adj.)</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>צִבּוּרִי</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>צִבּוּרִית</t>
-        </is>
-      </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>צִבּוּרִיִּים</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>צִבּוּרִיּוֹת</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr"/>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>adjective</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>café</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>קָפֶה</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr"/>
-      <c r="D222" s="2" t="inlineStr"/>
-      <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>some</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr"/>
-      <c r="C223" s="2" t="inlineStr"/>
-      <c r="D223" s="2" t="inlineStr"/>
-      <c r="E223" s="2" t="inlineStr"/>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>קְצָת</t>
-        </is>
-      </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t>quantifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>romanian</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr"/>
-      <c r="C224" s="3" t="inlineStr">
-        <is>
-          <t>רוֹמָנִית</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr"/>
-      <c r="E224" s="2" t="inlineStr"/>
-      <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="2" t="inlineStr">
-        <is>
-          <t>language</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>only, just</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr"/>
-      <c r="C225" s="2" t="inlineStr"/>
-      <c r="D225" s="2" t="inlineStr"/>
-      <c r="E225" s="2" t="inlineStr"/>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>רַק</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t>adverb</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>just a moment</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr"/>
-      <c r="C226" s="2" t="inlineStr"/>
-      <c r="D226" s="2" t="inlineStr"/>
-      <c r="E226" s="2" t="inlineStr"/>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>רַק רֶגַע</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>leftwards</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr"/>
-      <c r="C227" s="2" t="inlineStr"/>
-      <c r="D227" s="2" t="inlineStr"/>
-      <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>שְׂמֹאלָה</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>שִׁבְעָה</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>שֶׁבַע</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr"/>
-      <c r="E228" s="2" t="inlineStr"/>
-      <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="inlineStr">
-        <is>
-          <t>שִׁשָּׁה</t>
-        </is>
-      </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>שֵׁשׁ</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr"/>
-      <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>of</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr"/>
-      <c r="C230" s="2" t="inlineStr"/>
-      <c r="D230" s="2" t="inlineStr"/>
-      <c r="E230" s="2" t="inlineStr"/>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>שֶׁל</t>
-        </is>
-      </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>preposition</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr"/>
-      <c r="C231" s="2" t="inlineStr"/>
-      <c r="D231" s="2" t="inlineStr"/>
-      <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>שָׁלוֹם</t>
-        </is>
-      </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>greeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>שְׁלוֹשָׁה</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>שָׁלוֹשׁ</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr"/>
-      <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>there (direction)</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr"/>
-      <c r="C233" s="2" t="inlineStr"/>
-      <c r="D233" s="2" t="inlineStr"/>
-      <c r="E233" s="2" t="inlineStr"/>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>שָׁם</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>adverb</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>left (side)</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>שְׂמֹאל</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr"/>
-      <c r="D234" s="2" t="inlineStr"/>
-      <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>שְׁמוֹנָה</t>
-        </is>
-      </c>
-      <c r="C235" s="3" t="inlineStr">
-        <is>
-          <t>שְׁמוֹנֶה</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr"/>
-      <c r="E235" s="2" t="inlineStr"/>
-      <c r="F235" s="2" t="inlineStr"/>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="inlineStr">
-        <is>
-          <t>שְׁנַיִם</t>
-        </is>
-      </c>
-      <c r="C236" s="3" t="inlineStr">
-        <is>
-          <t>שְׁתַּיִם</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr"/>
-      <c r="E236" s="2" t="inlineStr"/>
-      <c r="F236" s="2" t="inlineStr"/>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr"/>
-      <c r="C237" s="3" t="inlineStr">
-        <is>
-          <t>שָׁעָה</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr"/>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>שָׁעוֹת</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr"/>
-      <c r="G237" s="2" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>thank you</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr"/>
-      <c r="C238" s="2" t="inlineStr"/>
-      <c r="D238" s="2" t="inlineStr"/>
-      <c r="E238" s="2" t="inlineStr"/>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>תּוֹדָה</t>
-        </is>
-      </c>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>phrase</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>date (fruit)</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="inlineStr">
-        <is>
-          <t>תָּמָר</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr"/>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>תְּמָרִים</t>
-        </is>
-      </c>
-      <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>תִּשְׁעָה</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>תֵּשַׁע</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr"/>
-      <c r="E240" s="2" t="inlineStr"/>
-      <c r="F240" s="2" t="inlineStr"/>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>which</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>אֵיזֶה</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="inlineStr">
-        <is>
-          <t>אֵיזוֹ</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>אֵילּוּ</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>אֵילּוּ</t>
-        </is>
-      </c>
-      <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>question word</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>sometimes</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr"/>
-      <c r="C242" s="2" t="inlineStr"/>
-      <c r="D242" s="2" t="inlineStr"/>
-      <c r="E242" s="2" t="inlineStr"/>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>לִפְעָמִים</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>adverb</t>
         </is>

--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2856,6 +2856,340 @@
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>סֵפֶר</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>סְפָרִים</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>garden; kindergarten</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>גַּן</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>גַּנִּים</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>coffee house; café</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>בֵּית קָפֶה</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>בָּתֵּי קָפֶה</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>construct noun phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>יֶלֶד</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>יַלְדָּה</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>יְלָדִים</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>יְלָדוֹת</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>internet</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>אִינְטֶרְנֶט</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>עִתּוֹנַאי</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>עִתּוֹנָאִית</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>עִתּוֹנָאִים</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>עִתּוֹנָאִיּוֹת</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>time; period</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>זְמַן</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>זְמַנִּים</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>הוֹרֶה</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>הוֹרִים</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>common-gender noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>intellectual</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>אִינְטֵלֶקְטוּאָל</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>אִינְטֵלֶקְטוּאָלִית</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>אִינְטֵלֶקְטוּאָלִים</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>אִינְטֵלֶקְטוּאָלִיּוֹת</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>הִיסְטוֹרְיָה</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>הִיסְטוֹרְיוֹת</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>philosopher</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>פִילוֹסוֹף</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>פִילוֹסוֹפִית</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>פִילוֹסוֹפִים</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>פִילוֹסוֹפִיּוֹת</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>טֶבַע</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="3" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>mostly singular</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>סִפּוּר</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>סִפּוּרִים</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>future</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>עָתִיד</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>עֲתִידִים</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3190,6 +3190,181 @@
       <c r="F128" s="2" t="n"/>
       <c r="G128" s="2" t="n"/>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>supermarket</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>סוּפֶּרְמַרְקֶט</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>סוּפֶּרְמַרְקֶטִים</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>בַּנְק</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>בַּנְקִים</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>אוּנִיבֶרְסִיטָה</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>אוּנִיבֶרְסִיטָאוֹת</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>kiosk</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>קִיּוֹסְק</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr"/>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>קִיּוֹסְקִים</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>theatre</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>תֵּיאַטְרוֹן</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>תֵּיאַטְרָאוֹת</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>source spelling: תיאטרון</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>giraffe</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>גִּ'ירָף</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>גִּ'ירָפָה</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>גִּ'ירָפוֹת</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>animal; loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>sandwich</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>סֶנְדְוִיץ׳</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -3323,18 +3323,18 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>גִּ'ירָף</t>
+          <t>גִּ׳ירָף</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>גִּ'ירָפָה</t>
+          <t>גִּ׳ירָפָה</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>גִּ'ירָפוֹת</t>
+          <t>גִּ׳ירָפוֹת</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>

--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3365,6 +3365,39 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>כֶּלֶב</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>כַּלְבָּה</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>כְּלָבִים</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>כַּלְבּוֹת</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3398,6 +3398,1423 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>melon (fruit)</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>מֶלוֹן</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>מֶלוֹנִים</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>fruit; homograph of hotel</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>kilo; kilogram</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>קִילוֹ</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>קִילוֹאִים</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>colloquial unit; full form: קילוגרם</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>strawberry</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>תּוּת</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>תּוּתִים</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>fruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>orange (fruit)</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>תַּפּוּז</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>תַּפּוּזִים</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>fruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>apple</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>תַּפּוּחַ</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>תַּפּוּחִים</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>fruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>fruit</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>פְּרִי</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>פֵּרוֹת</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>collective/count noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>vegetable</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>יָרָק</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>יְרָקוֹת</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>food noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>electronics</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>אֶלֶקְטְרוֹנִיקָה</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>singular collective</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>חֹדֶשׁ</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>חֳדָשִׁים</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>time noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>party</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>מְסִבָּה</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>מְסִבּוֹת</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>neighbour; neighbor</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>שָׁכֵן</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>שְׁכֵנָה</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>שְׁכֵנִים</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>שְׁכֵנוֹת</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>exam</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>בְּחִינָה</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="n"/>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>בְּחִינוֹת</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>school noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>פֶּרַח</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>פְּרָחִים</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>invitation</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>הַזְמָנָה</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>הַזְמָנוֹת</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>event noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>מָקוֹם</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>מְקוֹמוֹת</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="n"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>טִיּוּל</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>טִיּוּלִים</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>travel noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>conference</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>כֶּנֶס</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>כְּנָסִים</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>cinema</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>קוֹלְנוֹעַ</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="3" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>place; film medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>centre; center</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>מֶרְכָּז</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>מֶרְכָּזִים</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n"/>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>customer; client</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>לָקוֹחַ</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>לָקוֹחָה</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>לָקוֹחוֹת</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>לָקוֹחוֹת</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>common plural</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>שָׁנָה</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="n"/>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>שָׁנִים</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>time noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>אָחוּז</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>אֲחוּזִים</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>quantity noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>bicycle; bicycles</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>אוֹפַנַּיִם</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>plural/dual noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>grandfather</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>סַבָּא</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>סַבִּים</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n"/>
+      <c r="F160" s="2" t="n"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>family noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>grandmother</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>סָבְתָא</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="n"/>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>סָבְתּוֹת</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>family noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>קִנּוּחַ</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>קִנּוּחִים</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="n"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>food noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>desert</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>מִדְבָּר</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>מִדְבָּרִים</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>place</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>כַּדּוּר</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>כַּדּוּרִים</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>butter</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n"/>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>חֶמְאָה</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>food noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>notebook</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>מַחְבֶּרֶת</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="n"/>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>מַחְבָּרוֹת</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>school noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>language</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>שָׂפָה</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>שָׂפוֹת</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>abstract noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>mail; post</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>דֹּאַר</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="3" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>collective noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>package</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>חֲבִילָה</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>חֲבִילוֹת</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>shirt</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>חֻלְצָה</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>חֻלְצוֹת</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>clothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>seller</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>מוֹכֵר</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>מוֹכֶרֶת</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>מוֹכְרִים</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>מוֹכְרוֹת</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>מִבְחָן</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>מִבְחָנִים</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>school noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>exercise</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>תַּרְגִּיל</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>תַּרְגִּילִים</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>school noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>summer</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>קַיִץ</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="2" t="n"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>winter</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>חֹרֶף</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="n"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>autumn; fall</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>סְתָיו</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>אָבִיב</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>sofa</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>סַפָּה</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>סַפּוֹת</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>furniture</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>מִיקְרוֹגַל</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="3" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="n"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>appliance; loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>oven</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>תַּנּוּר</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>תַּנּוּרִים</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>appliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>refrigerator</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>מְקָרֵר</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>מְקָרְרִים</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="n"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>appliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>bedroom</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>חֲדַר שֵׁנָה</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>חַדְרֵי שֵׁנָה</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>construct noun phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>wardrobe; cupboard; closet</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>אָרוֹן</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>אֲרוֹנוֹת</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>furniture</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>kindergarten teacher (fem.)</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="n"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>גַּנֶּנֶת</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>גַּנָּנוֹת</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>person; feminine noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>holiday</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>חַג</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>חַגִּים</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="n"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>calendar noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>soldier</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>חַיָּל</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>חַיֶּלֶת</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>חַיָּלִים</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>חַיָּלוֹת</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>state; country</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>מְדִינָה</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="n"/>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>מְדִינוֹת</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>political noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>candle</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>נֵר</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>נֵרוֹת</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>אוֹטוֹבּוּס</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>אוֹטוֹבּוּסִים</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="2" t="n"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>vehicle; loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>מְכוֹנִית</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="n"/>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>מְכוֹנִיּוֹת</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="n"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>vehicle</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>siren</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>צְפִירָה</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="n"/>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>צְפִירוֹת</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>sound/event noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>ceremony</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>טֶקֶס</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>טְקָסִים</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="n"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>break; pause</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>הַפְסָקָה</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="n"/>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>הַפְסָקוֹת</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="n"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>time/event noun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/nouns.xlsx
+++ b/etc/hebrew/nouns.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4815,6 +4815,673 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>chocolate</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹקוֹלָד</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>food noun; loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>cheese</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>גְּבִינָה</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="n"/>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>גְּבִינוֹת</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="n"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>food noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>cheesecake</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>עוּגַת גְּבִינָה</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>עוּגוֹת גְּבִינָה</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="n"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>construct noun phrase</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>popsicle; ice lolly</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>אַרְטִיק</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>אַרְטִיקִים</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>food noun; loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>candy; sweet</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>סֻכָּרִיָּה</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="n"/>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>סֻכָּרִיּוֹת</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>food noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>bag; small bag</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n"/>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>שַׂקִּית</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="n"/>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>שַׂקִּיּוֹת</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>moon</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>יָרֵחַ</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>יְרֵחִים</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="n"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>astronomical noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>כּוֹכָב</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="n"/>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>כּוֹכָבִים</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="2" t="n"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>astronomical noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>braid; plait</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n"/>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>צַמָּה</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="n"/>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>צַמּוֹת</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="n"/>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>hair noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>freckle</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>נֶמֶשׁ</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="n"/>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>נְמָשִׁים</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n"/>
+      <c r="F203" s="2" t="n"/>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>body noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>dimple</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>גֻּמָּה</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="n"/>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>גֻּמּוֹת</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="n"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>body noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>father; dad</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>אַבָּא</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="n"/>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>אָבוֹת</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n"/>
+      <c r="F205" s="2" t="n"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>family noun; colloquial singular</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>aunt</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>דּוֹדָה</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>דּוֹדוֹת</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="n"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>family noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>sister</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n"/>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>אָחוֹת</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="n"/>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>אֲחָיוֹת</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="n"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>family noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>case; incident</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>מִקְרֶה</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n"/>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>מִקְרִים</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n"/>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>event noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>baby</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>תִּינוֹק</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>תִּינוֹקֶת</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>תִּינוֹקוֹת</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="n"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>person noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>door</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>דֶּלֶת</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="n"/>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>דְּלָתוֹת</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="n"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>חַלּוֹן</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="n"/>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>חַלּוֹנוֹת</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n"/>
+      <c r="F211" s="2" t="n"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>shoe</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>נַעַל</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="n"/>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>נַעֲלַיִם</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="n"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>dual/plural noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>trousers; pants</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n"/>
+      <c r="C213" s="2" t="n"/>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>מִכְנָסַיִם</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="n"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>plural/dual noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>רֹאשׁ</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>רָאשִׁים</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="n"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>body noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>hat</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>כּוֹבַע</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="n"/>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>כּוֹבָעִים</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n"/>
+      <c r="F215" s="2" t="n"/>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>clothing noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>כְּבִישׁ</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="n"/>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>כְּבִישִׁים</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n"/>
+      <c r="F216" s="2" t="n"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>place noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n"/>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>מְהִירוּת</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>מְהִירוּיוֹת</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="n"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>abstract noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>צַד</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="n"/>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>צְדָדִים</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n"/>
+      <c r="F218" s="2" t="n"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>spatial noun</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>cigarette</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n"/>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>סִיגַרְיָה</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>סִיגַרְיוֹת</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="n"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>loanword</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>עָשָׁן</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="n"/>
+      <c r="D220" s="3" t="n"/>
+      <c r="E220" s="2" t="n"/>
+      <c r="F220" s="2" t="n"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>mass noun</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
